--- a/artfynd/A 48462-2025 artfynd.xlsx
+++ b/artfynd/A 48462-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114565901</v>
+        <v>114565899</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430844</v>
+        <v>430596</v>
       </c>
       <c r="R2" t="n">
-        <v>7058650</v>
+        <v>7058209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114565902</v>
+        <v>114565900</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430862</v>
+        <v>430692</v>
       </c>
       <c r="R3" t="n">
-        <v>7058645</v>
+        <v>7058334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114565899</v>
+        <v>114565901</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430596</v>
+        <v>430844</v>
       </c>
       <c r="R4" t="n">
-        <v>7058209</v>
+        <v>7058650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114565900</v>
+        <v>114565902</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430692</v>
+        <v>430862</v>
       </c>
       <c r="R5" t="n">
-        <v>7058334</v>
+        <v>7058645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
